--- a/Proyectos/Fundamentos-de-Construccion/Solucion/PRESUPUESTO DE OBRA -FC- G3 (DILIGENCIADO).xlsx
+++ b/Proyectos/Fundamentos-de-Construccion/Solucion/PRESUPUESTO DE OBRA -FC- G3 (DILIGENCIADO).xlsx
@@ -841,7 +841,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="3">
         <f>SUM(F7:F11)</f>
-        <v>17249420.11</v>
+        <v>23570562.22</v>
       </c>
     </row>
     <row r="7" ht="26.4" customHeight="1" s="30">
@@ -861,14 +861,14 @@
         </is>
       </c>
       <c r="D7" s="37" t="n">
-        <v>118.91</v>
+        <v>162.29</v>
       </c>
       <c r="E7" s="38" t="n">
         <v>57938</v>
       </c>
       <c r="F7" s="8">
         <f>+D7*E7</f>
-        <v>6889407.58</v>
+        <v>9402758.02</v>
       </c>
     </row>
     <row r="8">
@@ -888,14 +888,14 @@
         </is>
       </c>
       <c r="D8" s="37" t="n">
-        <v>32.43</v>
+        <v>64.86</v>
       </c>
       <c r="E8" s="39" t="n">
         <v>129619</v>
       </c>
       <c r="F8" s="8">
         <f>+D8*E8</f>
-        <v>4203544.17</v>
+        <v>8407088.34</v>
       </c>
     </row>
     <row r="9" ht="26.4" customHeight="1" s="30">
@@ -915,14 +915,14 @@
         </is>
       </c>
       <c r="D9" s="37" t="n">
-        <v>12.18</v>
+        <v>6.85</v>
       </c>
       <c r="E9" s="38" t="n">
         <v>74250</v>
       </c>
       <c r="F9" s="8">
         <f>+D9*E9</f>
-        <v>904365.0</v>
+        <v>508612.5</v>
       </c>
     </row>
     <row r="10" ht="26.4" customHeight="1" s="30">
@@ -1591,7 +1591,7 @@
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="3">
         <f>SUM(F49:F51)</f>
-        <v>36601475.05</v>
+        <v>42194966.05</v>
       </c>
     </row>
     <row r="49">
@@ -1638,14 +1638,14 @@
         </is>
       </c>
       <c r="D50" s="37" t="n">
-        <v>168.2</v>
+        <v>336.4</v>
       </c>
       <c r="E50" s="38" t="n">
         <v>33255</v>
       </c>
       <c r="F50" s="8">
         <f>+D50*E50</f>
-        <v>5593491.0</v>
+        <v>11186982.0</v>
       </c>
     </row>
     <row r="51">
@@ -1697,7 +1697,7 @@
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="3">
         <f>SUM(F54:F55)</f>
-        <v>3683664.9000000004</v>
+        <v>7169283.300000001</v>
       </c>
     </row>
     <row r="54">
@@ -1717,14 +1717,14 @@
         </is>
       </c>
       <c r="D54" s="37" t="n">
-        <v>530.1</v>
+        <v>1031.7</v>
       </c>
       <c r="E54" s="38" t="n">
         <v>6949</v>
       </c>
       <c r="F54" s="8">
         <f>+D54*E54</f>
-        <v>3683664.9000000004</v>
+        <v>7169283.300000001</v>
       </c>
     </row>
     <row r="55">
@@ -1827,7 +1827,7 @@
       <c r="E62" s="41" t="n"/>
       <c r="F62" s="10">
         <f>SUM(F3:F60)/2</f>
-        <v>171251994.69</v>
+        <v>186652246.2</v>
       </c>
     </row>
     <row r="63">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F64" s="8">
         <f>+F62*E64</f>
-        <v>13700159.5752</v>
+        <v>14932179.695999999</v>
       </c>
     </row>
     <row r="65">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F65" s="8">
         <f>+E65*F62</f>
-        <v>5137559.8407</v>
+        <v>5599567.385999999</v>
       </c>
     </row>
     <row r="66">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="F66" s="8">
         <f>+F62*E66</f>
-        <v>8562599.7345</v>
+        <v>9332612.31</v>
       </c>
     </row>
     <row r="67">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F67" s="8">
         <f>+F66*E67</f>
-        <v>1626893.949555</v>
+        <v>1773196.3389</v>
       </c>
     </row>
     <row r="68">
@@ -1924,7 +1924,7 @@
       <c r="E69" s="41" t="n"/>
       <c r="F69" s="14">
         <f>SUM(F62:F67)</f>
-        <v>200279207.789955</v>
+        <v>218289801.9309</v>
       </c>
     </row>
     <row r="70"/>

--- a/Proyectos/Fundamentos-de-Construccion/Solucion/PRESUPUESTO DE OBRA -FC- G3 (DILIGENCIADO).xlsx
+++ b/Proyectos/Fundamentos-de-Construccion/Solucion/PRESUPUESTO DE OBRA -FC- G3 (DILIGENCIADO).xlsx
@@ -841,7 +841,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="3">
         <f>SUM(F7:F11)</f>
-        <v>23570562.22</v>
+        <v>20710590.26</v>
       </c>
     </row>
     <row r="7" ht="26.4" customHeight="1" s="30">
@@ -861,14 +861,14 @@
         </is>
       </c>
       <c r="D7" s="37" t="n">
-        <v>162.29</v>
+        <v>112.12</v>
       </c>
       <c r="E7" s="38" t="n">
         <v>57938</v>
       </c>
       <c r="F7" s="8">
         <f>+D7*E7</f>
-        <v>9402758.02</v>
+        <v>6496008.5600000005</v>
       </c>
     </row>
     <row r="8">
@@ -915,14 +915,14 @@
         </is>
       </c>
       <c r="D9" s="37" t="n">
-        <v>6.85</v>
+        <v>7.48</v>
       </c>
       <c r="E9" s="38" t="n">
         <v>74250</v>
       </c>
       <c r="F9" s="8">
         <f>+D9*E9</f>
-        <v>508612.5</v>
+        <v>555390.0</v>
       </c>
     </row>
     <row r="10" ht="26.4" customHeight="1" s="30">
@@ -1154,7 +1154,7 @@
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="3">
         <f>SUM(F23)</f>
-        <v>6438208.0</v>
+        <v>6602447.999999999</v>
       </c>
     </row>
     <row r="23" ht="26.4" customHeight="1" s="30">
@@ -1174,14 +1174,14 @@
         </is>
       </c>
       <c r="D23" s="37" t="n">
-        <v>7.84</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="E23" s="39" t="n">
         <v>821200</v>
       </c>
       <c r="F23" s="8">
         <f>+D23*E23</f>
-        <v>6438208.0</v>
+        <v>6602447.999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1414,7 +1414,7 @@
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="3">
         <f>SUM(F38:F39)</f>
-        <v>5502218.199999999</v>
+        <v>4476545.800000001</v>
       </c>
     </row>
     <row r="38">
@@ -1434,14 +1434,14 @@
         </is>
       </c>
       <c r="D38" s="37" t="n">
-        <v>791.8</v>
+        <v>644.2</v>
       </c>
       <c r="E38" s="38" t="n">
         <v>6949</v>
       </c>
       <c r="F38" s="8">
         <f>+D38*E38</f>
-        <v>5502218.199999999</v>
+        <v>4476545.800000001</v>
       </c>
     </row>
     <row r="39">
@@ -1591,7 +1591,7 @@
       <c r="E48" s="2" t="n"/>
       <c r="F48" s="3">
         <f>SUM(F49:F51)</f>
-        <v>42194966.05</v>
+        <v>43650158.199999996</v>
       </c>
     </row>
     <row r="49">
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="D49" s="37" t="n">
-        <v>402.75</v>
+        <v>416.64</v>
       </c>
       <c r="E49" s="38" t="n">
         <v>61345</v>
       </c>
       <c r="F49" s="8">
         <f>+D49*E49</f>
-        <v>24706698.75</v>
+        <v>25558780.8</v>
       </c>
     </row>
     <row r="50">
@@ -1638,14 +1638,14 @@
         </is>
       </c>
       <c r="D50" s="37" t="n">
-        <v>336.4</v>
+        <v>348</v>
       </c>
       <c r="E50" s="38" t="n">
         <v>33255</v>
       </c>
       <c r="F50" s="8">
         <f>+D50*E50</f>
-        <v>11186982.0</v>
+        <v>11572740.0</v>
       </c>
     </row>
     <row r="51">
@@ -1665,14 +1665,14 @@
         </is>
       </c>
       <c r="D51" s="37" t="n">
-        <v>261.79</v>
+        <v>270.82</v>
       </c>
       <c r="E51" s="38" t="n">
         <v>24070</v>
       </c>
       <c r="F51" s="8">
         <f>+D51*E51</f>
-        <v>6301285.300000001</v>
+        <v>6518637.399999999</v>
       </c>
     </row>
     <row r="52">
@@ -1697,7 +1697,7 @@
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="3">
         <f>SUM(F54:F55)</f>
-        <v>7169283.300000001</v>
+        <v>7415972.800000001</v>
       </c>
     </row>
     <row r="54">
@@ -1717,14 +1717,14 @@
         </is>
       </c>
       <c r="D54" s="37" t="n">
-        <v>1031.7</v>
+        <v>1067.2</v>
       </c>
       <c r="E54" s="38" t="n">
         <v>6949</v>
       </c>
       <c r="F54" s="8">
         <f>+D54*E54</f>
-        <v>7169283.300000001</v>
+        <v>7415972.800000001</v>
       </c>
     </row>
     <row r="55">
@@ -1827,7 +1827,7 @@
       <c r="E62" s="41" t="n"/>
       <c r="F62" s="10">
         <f>SUM(F3:F60)/2</f>
-        <v>186652246.2</v>
+        <v>184632723.48999998</v>
       </c>
     </row>
     <row r="63">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F64" s="8">
         <f>+F62*E64</f>
-        <v>14932179.695999999</v>
+        <v>14770617.879199998</v>
       </c>
     </row>
     <row r="65">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F65" s="8">
         <f>+E65*F62</f>
-        <v>5599567.385999999</v>
+        <v>5538981.704699999</v>
       </c>
     </row>
     <row r="66">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="F66" s="8">
         <f>+F62*E66</f>
-        <v>9332612.31</v>
+        <v>9231636.1745</v>
       </c>
     </row>
     <row r="67">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F67" s="8">
         <f>+F66*E67</f>
-        <v>1773196.3389</v>
+        <v>1754010.873155</v>
       </c>
     </row>
     <row r="68">
@@ -1924,7 +1924,7 @@
       <c r="E69" s="41" t="n"/>
       <c r="F69" s="14">
         <f>SUM(F62:F67)</f>
-        <v>218289801.9309</v>
+        <v>215927970.12155497</v>
       </c>
     </row>
     <row r="70"/>
